--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.32</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -660,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.41</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -742,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.38</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -824,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.33</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -906,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.35</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -988,15 +1008,19 @@
       <c r="K7" t="n">
         <v>1.27</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1070,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.39</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1102,6 +1130,760 @@
       </c>
       <c r="T8" t="n">
         <v>38.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ukrainian Persha Liga</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FC Kolos Kovalivka 2 x Oleksandria</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FC Kolos Kovalivka 2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Oleksandria</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>28.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Portuguese Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Farense x Chaves</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>English Women's Matches</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Durham (W) x Newcastle Utd (W)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Durham (W)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Newcastle Utd (W)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>28.94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Greek Super League 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pyrgos AFC x Panionios</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pyrgos AFC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Panionios</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="T12" t="n">
+        <v>25.81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sociedad B x Granada</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sociedad B</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>877</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austrian ÖFB Frauen Bundesliga</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SKN St. Polten (W) x Sturm Graz (W)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SKN St. Polten (W)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sturm Graz (W)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T14" t="n">
+        <v>41.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>English WSL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>West Ham United (W) x Chelsea (W)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>West Ham United (W)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Chelsea (W)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>596</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>200</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>23.88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>English WSL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Brighton (W) x Charlton (W)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Brighton (W)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Charlton (W)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>200</v>
+      </c>
+      <c r="S16" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="T16" t="n">
+        <v>27.28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UEFA Nations League D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Azerbaijan x Lithuania</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>726</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>200</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="T17" t="n">
+        <v>11.23</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1438,15 +1438,19 @@
       <c r="K12" t="n">
         <v>1.57</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,15 +1524,19 @@
       <c r="K13" t="n">
         <v>2.52</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1602,15 +1610,19 @@
       <c r="K14" t="n">
         <v>1.4</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1684,15 +1696,19 @@
       <c r="K15" t="n">
         <v>1.2</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1852,15 +1868,19 @@
       <c r="K17" t="n">
         <v>1.5</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1884,6 +1904,502 @@
       </c>
       <c r="T17" t="n">
         <v>11.23</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Croatian Cup</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Vukovar x Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vukovar</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>200</v>
+      </c>
+      <c r="S18" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="T18" t="n">
+        <v>21.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>UAE Presidents Cup</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Al-Arabi Umm Quwain x Al Oruba</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Al-Arabi Umm Quwain</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Al Oruba</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>200</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>11.57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Norwegian 2nd Division</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mjondalen x Traeff</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mjondalen</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Traeff</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>200</v>
+      </c>
+      <c r="S20" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T20" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Boston River x Juventud De Las Piedras</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Juventud De Las Piedras</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>200</v>
+      </c>
+      <c r="S21" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UEFA Nations League B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kosovo x Austria</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>200</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="T22" t="n">
+        <v>11.57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UEFA Nations League D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Malta x Andorra</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>19</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>338</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>200</v>
+      </c>
+      <c r="S23" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="T23" t="n">
+        <v>10.61</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2040,15 +2040,19 @@
       <c r="K19" t="n">
         <v>2.62</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2122,15 +2126,19 @@
       <c r="K20" t="n">
         <v>1.35</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2204,15 +2212,19 @@
       <c r="K21" t="n">
         <v>2.52</v>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2286,15 +2298,19 @@
       <c r="K22" t="n">
         <v>2.04</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2368,15 +2384,19 @@
       <c r="K23" t="n">
         <v>1.5</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2400,6 +2420,498 @@
       </c>
       <c r="T23" t="n">
         <v>10.61</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Las Palmas x Valladolid</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>200</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>11.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CD Castellon x AD Ceuta FC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CD Castellon</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AD Ceuta FC</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>200</v>
+      </c>
+      <c r="S25" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="T25" t="n">
+        <v>30.81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Costa Rican Liga de Ascenso</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ADR Jicaral x A.D. Cofutpa</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ADR Jicaral</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>A.D. Cofutpa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>200</v>
+      </c>
+      <c r="S26" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Friendlies International</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Morocco x Mali</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>456</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>200</v>
+      </c>
+      <c r="S27" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T27" t="n">
+        <v>41.52</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sportivo Italiano x Talleres (RE)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sportivo Italiano</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talleres (RE)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>200</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="T28" t="n">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Nacional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Chacarita x Patronato</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Chacarita</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>200</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="T29" t="n">
+        <v>10.32</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,15 +2470,19 @@
       <c r="K24" t="n">
         <v>2.66</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2552,15 +2556,19 @@
       <c r="K25" t="n">
         <v>1.29</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2634,15 +2642,19 @@
       <c r="K26" t="n">
         <v>1.25</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2716,15 +2728,19 @@
       <c r="K27" t="n">
         <v>1.35</v>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2798,15 +2814,19 @@
       <c r="K28" t="n">
         <v>1.49</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2880,15 +2900,19 @@
       <c r="K29" t="n">
         <v>1.49</v>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2912,6 +2936,510 @@
       </c>
       <c r="T29" t="n">
         <v>10.32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UEFA Nations League A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wales x Denmark</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Wales</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>17</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>200</v>
+      </c>
+      <c r="S30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>UEFA Nations League A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Netherlands x Serbia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>4643</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>200</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>23.88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Girona x Mallorca</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>16</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>200</v>
+      </c>
+      <c r="S32" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="T32" t="n">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CONCACAF Nations League C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bahamas x US Virgin Islands</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>US Virgin Islands</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>200</v>
+      </c>
+      <c r="S33" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="T33" t="n">
+        <v>45.48</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jamaican Premier League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Montego Bay United x Dunbeholden FC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dunbeholden FC</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>200</v>
+      </c>
+      <c r="S34" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T34" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Panamanian Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Herrera FC x Alianza FC (Pan)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Herrera FC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Alianza FC (Pan)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>200</v>
+      </c>
+      <c r="S35" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T35" t="n">
+        <v>29.84</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,32 +518,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indonesian Championship</t>
+          <t>Ukrainian Persha Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deltras Sidoarjo x Persiba Balikpapan</t>
+          <t>FC Kolos Kovalivka 2 x Oleksandria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Deltras Sidoarjo</t>
+          <t>FC Kolos Kovalivka 2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persiba Balikpapan</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -553,14 +553,14 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -590,32 +590,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ukrainian Persha Liga</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Kolos Kovalivka 2 x Oleksandria</t>
+          <t>Farense x Chaves</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Kolos Kovalivka 2</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Chaves</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -625,14 +625,14 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -662,32 +662,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Greek Super League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Farense x Chaves</t>
+          <t>Pyrgos AFC x Panionios</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pyrgos AFC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chaves</t>
+          <t>Panionios</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
@@ -734,32 +734,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greek Super League 2</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pyrgos AFC x Panionios</t>
+          <t>Sociedad B x Granada</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pyrgos AFC</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Panionios</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>1.57</v>
+        <v>2.52</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>130</v>
+        <v>877</v>
       </c>
     </row>
     <row r="6">
@@ -806,32 +806,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sociedad B x Granada</t>
+          <t>Mjondalen x Traeff</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Mjondalen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Traeff</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.52</v>
+        <v>1.35</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>877</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -878,27 +878,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Presidents Cup</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Arabi Umm Quwain x Al Oruba</t>
+          <t>Boston River x Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Arabi Umm Quwain</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Oruba</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -916,11 +916,11 @@
         <v>17.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -950,32 +950,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mjondalen x Traeff</t>
+          <t>Las Palmas x Valladolid</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mjondalen</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Traeff</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -985,19 +985,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -1022,32 +1022,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Boston River x Juventud De Las Piedras</t>
+          <t>CD Castellon x AD Ceuta FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.52</v>
+        <v>1.29</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>98</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -1094,32 +1094,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Las Palmas x Valladolid</t>
+          <t>Sportivo Italiano x Talleres (RE)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1129,19 +1129,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.66</v>
+        <v>1.49</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CD Castellon x AD Ceuta FC</t>
+          <t>Chacarita x Patronato</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Chacarita</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Ceuta FC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1201,19 +1201,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -1238,32 +1238,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Costa Rican Liga de Ascenso</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ADR Jicaral x A.D. Cofutpa</t>
+          <t>Girona x Mallorca</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ADR Jicaral</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A.D. Cofutpa</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1273,14 +1273,14 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1299,367 +1299,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Argentinian Primera B Metropolitana</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sportivo Italiano x Talleres (RE)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sportivo Italiano</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Talleres (RE)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Nacional</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Chacarita x Patronato</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Chacarita</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Spanish Segunda Division</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Girona x Mallorca</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>16</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
         <v>245</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jamaican Premier League</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Montego Bay United x Dunbeholden FC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dunbeholden FC</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Panamanian Premier League</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Herrera FC x Alianza FC (Pan)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Herrera FC</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Alianza FC (Pan)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,19 +558,15 @@
       <c r="K2" t="n">
         <v>1.52</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -590,32 +586,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Greek Super League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Farense x Chaves</t>
+          <t>Pyrgos AFC x Panionios</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Pyrgos AFC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chaves</t>
+          <t>Panionios</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -625,24 +621,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -651,7 +643,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4">
@@ -662,32 +654,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Greek Super League 2</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pyrgos AFC x Panionios</t>
+          <t>Mjondalen x Traeff</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pyrgos AFC</t>
+          <t>Mjondalen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Panionios</t>
+          <t>Traeff</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -697,24 +689,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
+        <v>1.35</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -723,7 +711,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>130</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -734,7 +722,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -744,22 +732,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sociedad B x Granada</t>
+          <t>CD Castellon x AD Ceuta FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -769,24 +757,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
+        <v>1.29</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -795,7 +779,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>877</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -806,32 +790,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norwegian 2nd Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mjondalen x Traeff</t>
+          <t>Sportivo Italiano x Talleres (RE)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjondalen</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Traeff</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -841,24 +825,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -867,7 +847,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -878,32 +858,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boston River x Juventud De Las Piedras</t>
+          <t>Chacarita x Patronato</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Chacarita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -913,24 +893,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -939,367 +915,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Spanish Segunda Division</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Las Palmas x Valladolid</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Spanish Segunda Division</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CD Castellon x AD Ceuta FC</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CD Castellon</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AD Ceuta FC</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Argentinian Primera B Metropolitana</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sportivo Italiano x Talleres (RE)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sportivo Italiano</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Talleres (RE)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Nacional</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Chacarita x Patronato</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Chacarita</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
         <v>139</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Spanish Segunda Division</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Girona x Mallorca</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-04.xlsx
@@ -558,15 +558,19 @@
       <c r="K2" t="n">
         <v>1.52</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -626,15 +630,19 @@
       <c r="K3" t="n">
         <v>1.57</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -697,12 +705,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -762,15 +770,19 @@
       <c r="K5" t="n">
         <v>1.29</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -830,15 +842,19 @@
       <c r="K6" t="n">
         <v>1.49</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -898,15 +914,19 @@
       <c r="K7" t="n">
         <v>1.49</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
